--- a/enrollment/fileTemplates/student&sectionTemplates/section(XLSX).xlsx
+++ b/enrollment/fileTemplates/student&sectionTemplates/section(XLSX).xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d725c04a17b73256/Documents/Programming/VSCode/CAPSTONE-preEnrollment/preEnrollmentV6.2/enrollment/fileTemplates/student^0sectionTemplates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7E41EB0-3EFC-47A2-B84F-A7BFFB84906F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="39" documentId="13_ncr:1_{C7E41EB0-3EFC-47A2-B84F-A7BFFB84906F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E995CC3F-82CE-4673-9E2B-20BCFA9467A1}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{32C72668-5EA3-4148-AB22-E6FC3855149B}"/>
   </bookViews>
@@ -20,23 +20,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="12">
-  <si>
-    <t>A</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="30">
   <si>
     <t>Enrolled</t>
   </si>
   <si>
-    <t>Jerry</t>
-  </si>
-  <si>
-    <t>Corazon</t>
-  </si>
-  <si>
-    <t>1st</t>
-  </si>
-  <si>
     <t>STUDENT NUMBER</t>
   </si>
   <si>
@@ -56,6 +44,72 @@
   </si>
   <si>
     <t>STATUS</t>
+  </si>
+  <si>
+    <t>Z</t>
+  </si>
+  <si>
+    <t>2nd</t>
+  </si>
+  <si>
+    <t>Jamorie</t>
+  </si>
+  <si>
+    <t>Corry</t>
+  </si>
+  <si>
+    <t>Ferry</t>
+  </si>
+  <si>
+    <t>Evelyn</t>
+  </si>
+  <si>
+    <t>Harold</t>
+  </si>
+  <si>
+    <t>Fundi</t>
+  </si>
+  <si>
+    <t>Dela Gueva</t>
+  </si>
+  <si>
+    <t>Emirates</t>
+  </si>
+  <si>
+    <t>Mercado</t>
+  </si>
+  <si>
+    <t>Dizon</t>
+  </si>
+  <si>
+    <t>Ryzza Mae</t>
+  </si>
+  <si>
+    <t>Constance Angeline</t>
+  </si>
+  <si>
+    <t>Yelena Arabia</t>
+  </si>
+  <si>
+    <t>Zalry Jean</t>
+  </si>
+  <si>
+    <t>Jumaira Queen</t>
+  </si>
+  <si>
+    <t>Residente</t>
+  </si>
+  <si>
+    <t>Severino</t>
+  </si>
+  <si>
+    <t>Al Gaib</t>
+  </si>
+  <si>
+    <t>Sait</t>
+  </si>
+  <si>
+    <t>Parat</t>
   </si>
 </sst>
 </file>
@@ -941,716 +995,356 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>7</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
-        <v>202310017</v>
+        <v>202110017</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2">
         <v>2</v>
       </c>
-      <c r="C2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
       <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" t="s">
         <v>0</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="G2" t="s">
-        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
-        <v>202310018</v>
+        <v>202110018</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3">
         <v>2</v>
       </c>
-      <c r="C3" t="s">
-        <v>3</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
       <c r="E3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G3" t="s">
         <v>0</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="G3" t="s">
-        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
-        <v>202310019</v>
+        <v>202110019</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4">
         <v>2</v>
       </c>
-      <c r="C4" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
       <c r="E4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G4" t="s">
         <v>0</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="G4" t="s">
-        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
-        <v>202310020</v>
+        <v>202110020</v>
       </c>
       <c r="B5" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5">
         <v>2</v>
       </c>
-      <c r="C5" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
       <c r="E5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" t="s">
         <v>0</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="G5" t="s">
-        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
-        <v>202310021</v>
+        <v>202110021</v>
       </c>
       <c r="B6" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6">
         <v>2</v>
       </c>
-      <c r="C6" t="s">
-        <v>3</v>
-      </c>
-      <c r="D6">
-        <v>1</v>
-      </c>
       <c r="E6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G6" t="s">
         <v>0</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="G6" t="s">
-        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
-        <v>202310022</v>
+        <v>202110022</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7">
         <v>2</v>
       </c>
-      <c r="C7" t="s">
-        <v>3</v>
-      </c>
-      <c r="D7">
-        <v>1</v>
-      </c>
       <c r="E7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G7" t="s">
         <v>0</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="G7" t="s">
-        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
-        <v>202310023</v>
+        <v>202110023</v>
       </c>
       <c r="B8" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8">
         <v>2</v>
       </c>
-      <c r="C8" t="s">
-        <v>3</v>
-      </c>
-      <c r="D8">
-        <v>1</v>
-      </c>
       <c r="E8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G8" t="s">
         <v>0</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="G8" t="s">
-        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
-        <v>202310024</v>
+        <v>202110024</v>
       </c>
       <c r="B9" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" t="s">
+        <v>27</v>
+      </c>
+      <c r="D9">
         <v>2</v>
       </c>
-      <c r="C9" t="s">
-        <v>3</v>
-      </c>
-      <c r="D9">
-        <v>1</v>
-      </c>
       <c r="E9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G9" t="s">
         <v>0</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="G9" t="s">
-        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
-        <v>202310025</v>
+        <v>202110025</v>
       </c>
       <c r="B10" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" t="s">
+        <v>28</v>
+      </c>
+      <c r="D10">
         <v>2</v>
       </c>
-      <c r="C10" t="s">
-        <v>3</v>
-      </c>
-      <c r="D10">
-        <v>1</v>
-      </c>
       <c r="E10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G10" t="s">
         <v>0</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="G10" t="s">
-        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
-        <v>202310026</v>
+        <v>202110026</v>
       </c>
       <c r="B11" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" t="s">
+        <v>29</v>
+      </c>
+      <c r="D11">
         <v>2</v>
       </c>
-      <c r="C11" t="s">
-        <v>3</v>
-      </c>
-      <c r="D11">
-        <v>1</v>
-      </c>
       <c r="E11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G11" t="s">
         <v>0</v>
       </c>
-      <c r="F11" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="G11" t="s">
-        <v>1</v>
-      </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="2">
-        <v>202310027</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C12" t="s">
-        <v>3</v>
-      </c>
-      <c r="D12">
-        <v>1</v>
-      </c>
-      <c r="E12" t="s">
-        <v>0</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="G12" t="s">
-        <v>1</v>
-      </c>
+      <c r="A12" s="2"/>
+      <c r="B12" s="3"/>
+      <c r="F12" s="2"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="2">
-        <v>202310028</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C13" t="s">
-        <v>3</v>
-      </c>
-      <c r="D13">
-        <v>1</v>
-      </c>
-      <c r="E13" t="s">
-        <v>0</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="G13" t="s">
-        <v>1</v>
-      </c>
+      <c r="A13" s="2"/>
+      <c r="B13" s="3"/>
+      <c r="F13" s="2"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="2">
-        <v>202310029</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C14" t="s">
-        <v>3</v>
-      </c>
-      <c r="D14">
-        <v>1</v>
-      </c>
-      <c r="E14" t="s">
-        <v>0</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="G14" t="s">
-        <v>1</v>
-      </c>
+      <c r="A14" s="2"/>
+      <c r="B14" s="3"/>
+      <c r="F14" s="2"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" s="2">
-        <v>202310030</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C15" t="s">
-        <v>3</v>
-      </c>
-      <c r="D15">
-        <v>1</v>
-      </c>
-      <c r="E15" t="s">
-        <v>0</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="G15" t="s">
-        <v>1</v>
-      </c>
+      <c r="A15" s="2"/>
+      <c r="B15" s="3"/>
+      <c r="F15" s="2"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="2">
-        <v>202310031</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C16" t="s">
-        <v>3</v>
-      </c>
-      <c r="D16">
-        <v>1</v>
-      </c>
-      <c r="E16" t="s">
-        <v>0</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="G16" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A17" s="2">
-        <v>202310032</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C17" t="s">
-        <v>3</v>
-      </c>
-      <c r="D17">
-        <v>1</v>
-      </c>
-      <c r="E17" t="s">
-        <v>0</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="G17" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A18" s="2">
-        <v>202310033</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C18" t="s">
-        <v>3</v>
-      </c>
-      <c r="D18">
-        <v>1</v>
-      </c>
-      <c r="E18" t="s">
-        <v>0</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="G18" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A19" s="2">
-        <v>202310034</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C19" t="s">
-        <v>3</v>
-      </c>
-      <c r="D19">
-        <v>1</v>
-      </c>
-      <c r="E19" t="s">
-        <v>0</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="G19" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A20" s="2">
-        <v>202310035</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C20" t="s">
-        <v>3</v>
-      </c>
-      <c r="D20">
-        <v>1</v>
-      </c>
-      <c r="E20" t="s">
-        <v>0</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="G20" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A21" s="2">
-        <v>202310036</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C21" t="s">
-        <v>3</v>
-      </c>
-      <c r="D21">
-        <v>1</v>
-      </c>
-      <c r="E21" t="s">
-        <v>0</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="G21" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A22" s="2">
-        <v>202310037</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C22" t="s">
-        <v>3</v>
-      </c>
-      <c r="D22">
-        <v>1</v>
-      </c>
-      <c r="E22" t="s">
-        <v>0</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="G22" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A23" s="2">
-        <v>202310038</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C23" t="s">
-        <v>3</v>
-      </c>
-      <c r="D23">
-        <v>1</v>
-      </c>
-      <c r="E23" t="s">
-        <v>0</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="G23" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A24" s="2">
-        <v>202310039</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C24" t="s">
-        <v>3</v>
-      </c>
-      <c r="D24">
-        <v>1</v>
-      </c>
-      <c r="E24" t="s">
-        <v>0</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="G24" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A25" s="2">
-        <v>202310040</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C25" t="s">
-        <v>3</v>
-      </c>
-      <c r="D25">
-        <v>1</v>
-      </c>
-      <c r="E25" t="s">
-        <v>0</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="G25" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A26" s="2">
-        <v>202310041</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C26" t="s">
-        <v>3</v>
-      </c>
-      <c r="D26">
-        <v>1</v>
-      </c>
-      <c r="E26" t="s">
-        <v>0</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="G26" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A27" s="2">
-        <v>202310042</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C27" t="s">
-        <v>3</v>
-      </c>
-      <c r="D27">
-        <v>1</v>
-      </c>
-      <c r="E27" t="s">
-        <v>0</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="G27" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A28" s="2">
-        <v>202310043</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C28" t="s">
-        <v>3</v>
-      </c>
-      <c r="D28">
-        <v>1</v>
-      </c>
-      <c r="E28" t="s">
-        <v>0</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="G28" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A29" s="2">
-        <v>202310044</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C29" t="s">
-        <v>3</v>
-      </c>
-      <c r="D29">
-        <v>1</v>
-      </c>
-      <c r="E29" t="s">
-        <v>0</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="G29" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A30" s="2">
-        <v>202310045</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C30" t="s">
-        <v>3</v>
-      </c>
-      <c r="D30">
-        <v>1</v>
-      </c>
-      <c r="E30" t="s">
-        <v>0</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="G30" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A31" s="2">
-        <v>202310046</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C31" t="s">
-        <v>3</v>
-      </c>
-      <c r="D31">
-        <v>1</v>
-      </c>
-      <c r="E31" t="s">
-        <v>0</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="G31" t="s">
-        <v>1</v>
-      </c>
+      <c r="A16" s="2"/>
+      <c r="B16" s="3"/>
+      <c r="F16" s="2"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17" s="2"/>
+      <c r="B17" s="3"/>
+      <c r="F17" s="2"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18" s="2"/>
+      <c r="B18" s="3"/>
+      <c r="F18" s="2"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19" s="2"/>
+      <c r="B19" s="3"/>
+      <c r="F19" s="2"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20" s="2"/>
+      <c r="B20" s="3"/>
+      <c r="F20" s="2"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A21" s="2"/>
+      <c r="B21" s="3"/>
+      <c r="F21" s="2"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A22" s="2"/>
+      <c r="B22" s="3"/>
+      <c r="F22" s="2"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A23" s="2"/>
+      <c r="B23" s="3"/>
+      <c r="F23" s="2"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A24" s="2"/>
+      <c r="B24" s="3"/>
+      <c r="F24" s="2"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A25" s="2"/>
+      <c r="B25" s="3"/>
+      <c r="F25" s="2"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A26" s="2"/>
+      <c r="B26" s="3"/>
+      <c r="F26" s="2"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A27" s="2"/>
+      <c r="B27" s="3"/>
+      <c r="F27" s="2"/>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A28" s="2"/>
+      <c r="B28" s="3"/>
+      <c r="F28" s="2"/>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A29" s="2"/>
+      <c r="B29" s="3"/>
+      <c r="F29" s="2"/>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A30" s="2"/>
+      <c r="B30" s="3"/>
+      <c r="F30" s="2"/>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A31" s="2"/>
+      <c r="B31" s="3"/>
+      <c r="F31" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
